--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_030.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_030.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="155">
   <si>
     <t>Sezione</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto nascita intestatario</t>
@@ -529,11 +535,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.05859375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -2820,53 +2826,53 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C100" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>100</v>
@@ -2875,7 +2881,7 @@
         <v>33</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>101</v>
@@ -2884,12 +2890,12 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>102</v>
@@ -2898,7 +2904,7 @@
         <v>33</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>103</v>
@@ -2907,12 +2913,12 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>104</v>
@@ -2921,7 +2927,7 @@
         <v>33</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>105</v>
@@ -2930,12 +2936,12 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>106</v>
@@ -2944,44 +2950,44 @@
         <v>33</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>109</v>
@@ -2990,44 +2996,44 @@
         <v>33</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>112</v>
@@ -3036,7 +3042,7 @@
         <v>33</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>113</v>
@@ -3045,12 +3051,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>114</v>
@@ -3059,7 +3065,7 @@
         <v>33</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>115</v>
@@ -3068,12 +3074,12 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>116</v>
@@ -3082,7 +3088,7 @@
         <v>33</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>117</v>
@@ -3091,44 +3097,44 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C112" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B113" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>123</v>
@@ -3142,7 +3148,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>124</v>
@@ -3151,7 +3157,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>125</v>
@@ -3165,19 +3171,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3188,16 +3194,16 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>128</v>
@@ -3211,16 +3217,16 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>130</v>
@@ -3234,7 +3240,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>131</v>
@@ -3243,7 +3249,7 @@
         <v>33</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>132</v>
@@ -3257,19 +3263,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3280,19 +3286,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3303,16 +3309,16 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>138</v>
@@ -3326,16 +3332,16 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>140</v>
@@ -3349,16 +3355,16 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>142</v>
@@ -3372,19 +3378,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3395,19 +3401,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3418,19 +3424,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3441,16 +3447,16 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>148</v>
@@ -3464,7 +3470,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>149</v>
@@ -3473,7 +3479,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>150</v>
@@ -3487,7 +3493,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>151</v>
@@ -3496,7 +3502,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>152</v>
@@ -3505,6 +3511,29 @@
         <v>10</v>
       </c>
       <c r="G129" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" s="2" t="s">
         <v>19</v>
       </c>
     </row>
